--- a/tests/fixtures/cores.xlsx
+++ b/tests/fixtures/cores.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Exemplo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{0109A3C7-3B61-48FF-9F19-478B0662E973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -2986,10 +2986,10 @@
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="E5" dT="2026-07-13T14:05:01.39" personId="{E95E8EAA-183E-49E9-B800-72A393CDF372}" id="{13F3A532-C9D8-45E9-8F90-14493AB154A2}">
-    <text>valor p/Bruna para conta Jhon</text>
+    <text>comentario de teste</text>
   </threadedComment>
   <threadedComment ref="E12" dT="2026-05-20T14:23:38.31" personId="{E95E8EAA-183E-49E9-B800-72A393CDF372}" id="{59788B5C-0757-4D79-81A5-E1811E487993}">
-    <text>GRUPO M8 DOCUMENTOS</text>
+    <text>comentario de teste</text>
   </threadedComment>
 </ThreadedComments>
 </file>

--- a/tests/fixtures/cores.xlsx
+++ b/tests/fixtures/cores.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>REF</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>COR DESCONHECIDA</t>
+  </si>
+  <si>
+    <t>FT998.26</t>
+  </si>
+  <si>
+    <t>SEM COR</t>
   </si>
 </sst>
 </file>
@@ -2996,7 +3002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB5C4C1-7B16-415C-9319-3F9A3F1843AE}">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="31.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.140625" style="162" bestFit="1" customWidth="1"/>
@@ -3176,16 +3182,28 @@
       <c r="L10" s="281"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="163" t="s">
+      <c r="A11" s="169" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="163" t="s">
+      <c r="B11" s="169" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="163">
+      <c r="I11" s="169">
         <v>46244</v>
       </c>
-      <c r="L11" s="163"/>
+      <c r="L11" s="169"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="163" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="163" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="163">
+        <v>46244</v>
+      </c>
+      <c r="L12" s="163"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
